--- a/PIB_Brasil_v2.xlsx
+++ b/PIB_Brasil_v2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cgbent-my.sharepoint.com/personal/eduardo_diamandis_zennohglobal_com/Documents/ZGC-PBI Research - Documents/Dataset Data Files/Weather_maps/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="70" documentId="11_F37763B38E9F6304BDFCAC06225064B5EB9AE21C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E4F66823-7942-4E55-954A-E0FE4095D512}"/>
+  <xr:revisionPtr revIDLastSave="72" documentId="11_F37763B38E9F6304BDFCAC06225064B5EB9AE21C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{327D1ACA-E09F-405A-97BB-BAC6BE1E059F}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-15" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
